--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T15:49:35+00:00</t>
+    <t>2026-01-30T11:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T11:01:37+00:00</t>
+    <t>2026-01-30T14:32:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T14:32:15+00:00</t>
+    <t>2026-02-09T09:12:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Task|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Task</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -733,7 +733,7 @@
     <t>Task.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-careplan-projet-personnalise|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-careplan-projet-personnalise)
 </t>
   </si>
   <si>
@@ -928,7 +928,7 @@
     <t>The title (eg "My Tasks", "Outstanding Tasks for Patient X") should go into the code.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j366-statut-bilan-projet-personnalise-ms|20250415120000</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j366-statut-bilan-projet-personnalise-ms</t>
   </si>
   <si>
     <t>categorieBilan</t>
@@ -1516,7 +1516,7 @@
     <t>Inputs are named to enable task automation to bind data and pass it from one task to the next.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/input-tddui-task-bilan-valueset|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-task-input-bilan</t>
   </si>
   <si>
     <t>Task.input.value[x]</t>
@@ -1558,7 +1558,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="perimetre"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1593,7 +1593,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="problematique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1628,7 +1628,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="invite"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1663,7 +1663,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="pieceJointe"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1672,7 +1672,7 @@
     <t>Task.input:pieceJointe.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-document-reference|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-document-reference)
 </t>
   </si>
   <si>
@@ -1699,7 +1699,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="dateProchainBilan"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1731,7 +1731,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="synthesePreparationBilan"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1790,7 +1790,7 @@
     <t>authorReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-related-person-contact)
 </t>
   </si>
   <si>
@@ -1873,7 +1873,7 @@
     <t>Outputs are named to enable task automation to bind data and pass it from one task to the next.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/output-tddui-task-bilan-valueset|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-task-output-bilan</t>
   </si>
   <si>
     <t>Task.output.value[x]</t>
@@ -1911,7 +1911,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/output-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-output-bilan"/&gt;
     &lt;code value="syntheseBilan"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -2247,7 +2247,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="113.34765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="81.8203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.29296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T09:12:46+00:00</t>
+    <t>2026-02-10T10:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:23:53+00:00</t>
+    <t>2026-02-11T15:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:25:25+00:00</t>
+    <t>2026-02-16T10:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:19:26+00:00</t>
+    <t>2026-02-23T14:19:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T14:19:51+00:00</t>
+    <t>2026-02-24T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:04:30+00:00</t>
+    <t>2026-02-26T15:31:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
